--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135710600</v>
       </c>
       <c r="B2" t="n">
-        <v>92227</v>
+        <v>92229</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135710603</v>
       </c>
       <c r="B3" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135710605</v>
       </c>
       <c r="B4" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135710614</v>
       </c>
       <c r="B5" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135710617</v>
       </c>
       <c r="B6" t="n">
-        <v>96486</v>
+        <v>96488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135710620</v>
       </c>
       <c r="B7" t="n">
-        <v>93345</v>
+        <v>93347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135710601</v>
       </c>
       <c r="B8" t="n">
-        <v>93349</v>
+        <v>93351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135710622</v>
       </c>
       <c r="B9" t="n">
-        <v>93349</v>
+        <v>93351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135710604</v>
       </c>
       <c r="B10" t="n">
-        <v>93034</v>
+        <v>93036</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>135710608</v>
       </c>
       <c r="B28" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>135710610</v>
       </c>
       <c r="B29" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>135710618</v>
       </c>
       <c r="B30" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135710611</v>
       </c>
       <c r="B31" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>135710616</v>
       </c>
       <c r="B32" t="n">
-        <v>99296</v>
+        <v>99298</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>135710606</v>
       </c>
       <c r="B33" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>135710613</v>
       </c>
       <c r="B34" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135710600</v>
       </c>
       <c r="B2" t="n">
-        <v>92229</v>
+        <v>92243</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135710603</v>
       </c>
       <c r="B3" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135710605</v>
       </c>
       <c r="B4" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135710614</v>
       </c>
       <c r="B5" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135710617</v>
       </c>
       <c r="B6" t="n">
-        <v>96488</v>
+        <v>96505</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135710620</v>
       </c>
       <c r="B7" t="n">
-        <v>93347</v>
+        <v>93362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135710601</v>
       </c>
       <c r="B8" t="n">
-        <v>93351</v>
+        <v>93366</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135710622</v>
       </c>
       <c r="B9" t="n">
-        <v>93351</v>
+        <v>93366</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135710604</v>
       </c>
       <c r="B10" t="n">
-        <v>93036</v>
+        <v>93051</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>135710625</v>
       </c>
       <c r="B11" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>135710602</v>
       </c>
       <c r="B12" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>135710623</v>
       </c>
       <c r="B13" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>135710627</v>
       </c>
       <c r="B14" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>135710631</v>
       </c>
       <c r="B15" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>135710612</v>
       </c>
       <c r="B16" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>135710629</v>
       </c>
       <c r="B17" t="n">
-        <v>78445</v>
+        <v>78447</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135710595</v>
       </c>
       <c r="B18" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>135710597</v>
       </c>
       <c r="B19" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>135710633</v>
       </c>
       <c r="B20" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>135710634</v>
       </c>
       <c r="B21" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>135710635</v>
       </c>
       <c r="B22" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>135710594</v>
       </c>
       <c r="B23" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>135710596</v>
       </c>
       <c r="B24" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>135710615</v>
       </c>
       <c r="B25" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>135710619</v>
       </c>
       <c r="B26" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>135710621</v>
       </c>
       <c r="B27" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>135710608</v>
       </c>
       <c r="B28" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>135710610</v>
       </c>
       <c r="B29" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>135710618</v>
       </c>
       <c r="B30" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135710611</v>
       </c>
       <c r="B31" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>135710616</v>
       </c>
       <c r="B32" t="n">
-        <v>99298</v>
+        <v>99315</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>135710606</v>
       </c>
       <c r="B33" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>135710613</v>
       </c>
       <c r="B34" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>135710626</v>
       </c>
       <c r="B35" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>135710628</v>
       </c>
       <c r="B36" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>135710630</v>
       </c>
       <c r="B37" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>135710607</v>
       </c>
       <c r="B38" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>135710624</v>
       </c>
       <c r="B39" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>135710632</v>
       </c>
       <c r="B40" t="n">
-        <v>79464</v>
+        <v>79466</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135710600</v>
       </c>
       <c r="B2" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135710603</v>
       </c>
       <c r="B3" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135710605</v>
       </c>
       <c r="B4" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135710614</v>
       </c>
       <c r="B5" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135710617</v>
       </c>
       <c r="B6" t="n">
-        <v>96505</v>
+        <v>96506</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135710620</v>
       </c>
       <c r="B7" t="n">
-        <v>93362</v>
+        <v>93363</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135710601</v>
       </c>
       <c r="B8" t="n">
-        <v>93366</v>
+        <v>93367</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135710622</v>
       </c>
       <c r="B9" t="n">
-        <v>93366</v>
+        <v>93367</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135710604</v>
       </c>
       <c r="B10" t="n">
-        <v>93051</v>
+        <v>93052</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>135710625</v>
       </c>
       <c r="B11" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>135710602</v>
       </c>
       <c r="B12" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>135710623</v>
       </c>
       <c r="B13" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>135710627</v>
       </c>
       <c r="B14" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>135710631</v>
       </c>
       <c r="B15" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>135710612</v>
       </c>
       <c r="B16" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>135710629</v>
       </c>
       <c r="B17" t="n">
-        <v>78447</v>
+        <v>78448</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>135710608</v>
       </c>
       <c r="B28" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>135710610</v>
       </c>
       <c r="B29" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>135710618</v>
       </c>
       <c r="B30" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135710611</v>
       </c>
       <c r="B31" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>135710616</v>
       </c>
       <c r="B32" t="n">
-        <v>99315</v>
+        <v>99316</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>135710606</v>
       </c>
       <c r="B33" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>135710613</v>
       </c>
       <c r="B34" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>135710626</v>
       </c>
       <c r="B35" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>135710628</v>
       </c>
       <c r="B36" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>135710630</v>
       </c>
       <c r="B37" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>135710607</v>
       </c>
       <c r="B38" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>135710624</v>
       </c>
       <c r="B39" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>135710632</v>
       </c>
       <c r="B40" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135710600</v>
       </c>
       <c r="B2" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135710603</v>
       </c>
       <c r="B3" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135710605</v>
       </c>
       <c r="B4" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135710614</v>
       </c>
       <c r="B5" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135710617</v>
       </c>
       <c r="B6" t="n">
-        <v>96506</v>
+        <v>96507</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135710620</v>
       </c>
       <c r="B7" t="n">
-        <v>93363</v>
+        <v>93364</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135710601</v>
       </c>
       <c r="B8" t="n">
-        <v>93367</v>
+        <v>93368</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135710622</v>
       </c>
       <c r="B9" t="n">
-        <v>93367</v>
+        <v>93368</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135710604</v>
       </c>
       <c r="B10" t="n">
-        <v>93052</v>
+        <v>93053</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>135710608</v>
       </c>
       <c r="B28" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>135710610</v>
       </c>
       <c r="B29" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>135710618</v>
       </c>
       <c r="B30" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135710611</v>
       </c>
       <c r="B31" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>135710616</v>
       </c>
       <c r="B32" t="n">
-        <v>99316</v>
+        <v>99317</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>135710606</v>
       </c>
       <c r="B33" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>135710613</v>
       </c>
       <c r="B34" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135710600</v>
       </c>
       <c r="B2" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135710603</v>
       </c>
       <c r="B3" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135710605</v>
       </c>
       <c r="B4" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135710614</v>
       </c>
       <c r="B5" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135710617</v>
       </c>
       <c r="B6" t="n">
-        <v>96507</v>
+        <v>96508</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135710620</v>
       </c>
       <c r="B7" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135710601</v>
       </c>
       <c r="B8" t="n">
-        <v>93368</v>
+        <v>93369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135710622</v>
       </c>
       <c r="B9" t="n">
-        <v>93368</v>
+        <v>93369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135710604</v>
       </c>
       <c r="B10" t="n">
-        <v>93053</v>
+        <v>93054</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>135710625</v>
       </c>
       <c r="B11" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>135710602</v>
       </c>
       <c r="B12" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>135710623</v>
       </c>
       <c r="B13" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>135710627</v>
       </c>
       <c r="B14" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>135710631</v>
       </c>
       <c r="B15" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>135710612</v>
       </c>
       <c r="B16" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>135710629</v>
       </c>
       <c r="B17" t="n">
-        <v>78448</v>
+        <v>78449</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135710595</v>
       </c>
       <c r="B18" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>135710597</v>
       </c>
       <c r="B19" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>135710633</v>
       </c>
       <c r="B20" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>135710634</v>
       </c>
       <c r="B21" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>135710635</v>
       </c>
       <c r="B22" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>135710594</v>
       </c>
       <c r="B23" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>135710596</v>
       </c>
       <c r="B24" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>135710615</v>
       </c>
       <c r="B25" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>135710619</v>
       </c>
       <c r="B26" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>135710621</v>
       </c>
       <c r="B27" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>135710608</v>
       </c>
       <c r="B28" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>135710610</v>
       </c>
       <c r="B29" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>135710618</v>
       </c>
       <c r="B30" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135710611</v>
       </c>
       <c r="B31" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>135710616</v>
       </c>
       <c r="B32" t="n">
-        <v>99317</v>
+        <v>99318</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>135710606</v>
       </c>
       <c r="B33" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>135710613</v>
       </c>
       <c r="B34" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>135710626</v>
       </c>
       <c r="B35" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>135710628</v>
       </c>
       <c r="B36" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>135710630</v>
       </c>
       <c r="B37" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>135710607</v>
       </c>
       <c r="B38" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>135710624</v>
       </c>
       <c r="B39" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>135710632</v>
       </c>
       <c r="B40" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135710600</v>
       </c>
       <c r="B2" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135710603</v>
       </c>
       <c r="B3" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135710605</v>
       </c>
       <c r="B4" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135710614</v>
       </c>
       <c r="B5" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135710617</v>
       </c>
       <c r="B6" t="n">
-        <v>96508</v>
+        <v>96514</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135710620</v>
       </c>
       <c r="B7" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135710601</v>
       </c>
       <c r="B8" t="n">
-        <v>93369</v>
+        <v>93375</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135710622</v>
       </c>
       <c r="B9" t="n">
-        <v>93369</v>
+        <v>93375</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135710604</v>
       </c>
       <c r="B10" t="n">
-        <v>93054</v>
+        <v>93060</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>135710625</v>
       </c>
       <c r="B11" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>135710602</v>
       </c>
       <c r="B12" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>135710623</v>
       </c>
       <c r="B13" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>135710627</v>
       </c>
       <c r="B14" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>135710631</v>
       </c>
       <c r="B15" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>135710612</v>
       </c>
       <c r="B16" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>135710629</v>
       </c>
       <c r="B17" t="n">
-        <v>78449</v>
+        <v>78453</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135710595</v>
       </c>
       <c r="B18" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>135710597</v>
       </c>
       <c r="B19" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>135710633</v>
       </c>
       <c r="B20" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>135710634</v>
       </c>
       <c r="B21" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>135710635</v>
       </c>
       <c r="B22" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>135710594</v>
       </c>
       <c r="B23" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>135710596</v>
       </c>
       <c r="B24" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>135710615</v>
       </c>
       <c r="B25" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>135710619</v>
       </c>
       <c r="B26" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>135710621</v>
       </c>
       <c r="B27" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>135710608</v>
       </c>
       <c r="B28" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>135710610</v>
       </c>
       <c r="B29" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>135710618</v>
       </c>
       <c r="B30" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135710611</v>
       </c>
       <c r="B31" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>135710616</v>
       </c>
       <c r="B32" t="n">
-        <v>99318</v>
+        <v>99324</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>135710606</v>
       </c>
       <c r="B33" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>135710613</v>
       </c>
       <c r="B34" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>135710626</v>
       </c>
       <c r="B35" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>135710628</v>
       </c>
       <c r="B36" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>135710630</v>
       </c>
       <c r="B37" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>135710607</v>
       </c>
       <c r="B38" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>135710624</v>
       </c>
       <c r="B39" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>135710632</v>
       </c>
       <c r="B40" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135710600</v>
       </c>
       <c r="B2" t="n">
-        <v>92252</v>
+        <v>92253</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135710603</v>
       </c>
       <c r="B3" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135710605</v>
       </c>
       <c r="B4" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135710614</v>
       </c>
       <c r="B5" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135710617</v>
       </c>
       <c r="B6" t="n">
-        <v>96514</v>
+        <v>96515</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135710620</v>
       </c>
       <c r="B7" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135710601</v>
       </c>
       <c r="B8" t="n">
-        <v>93375</v>
+        <v>93376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135710622</v>
       </c>
       <c r="B9" t="n">
-        <v>93375</v>
+        <v>93376</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135710604</v>
       </c>
       <c r="B10" t="n">
-        <v>93060</v>
+        <v>93061</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>135710625</v>
       </c>
       <c r="B11" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>135710602</v>
       </c>
       <c r="B12" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>135710623</v>
       </c>
       <c r="B13" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>135710627</v>
       </c>
       <c r="B14" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>135710631</v>
       </c>
       <c r="B15" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>135710612</v>
       </c>
       <c r="B16" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>135710629</v>
       </c>
       <c r="B17" t="n">
-        <v>78453</v>
+        <v>78454</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135710595</v>
       </c>
       <c r="B18" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>135710597</v>
       </c>
       <c r="B19" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>135710633</v>
       </c>
       <c r="B20" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>135710634</v>
       </c>
       <c r="B21" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>135710635</v>
       </c>
       <c r="B22" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>135710594</v>
       </c>
       <c r="B23" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>135710596</v>
       </c>
       <c r="B24" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>135710615</v>
       </c>
       <c r="B25" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>135710619</v>
       </c>
       <c r="B26" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>135710621</v>
       </c>
       <c r="B27" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>135710608</v>
       </c>
       <c r="B28" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>135710610</v>
       </c>
       <c r="B29" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>135710618</v>
       </c>
       <c r="B30" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135710611</v>
       </c>
       <c r="B31" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>135710616</v>
       </c>
       <c r="B32" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>135710606</v>
       </c>
       <c r="B33" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>135710613</v>
       </c>
       <c r="B34" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>135710626</v>
       </c>
       <c r="B35" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>135710628</v>
       </c>
       <c r="B36" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>135710630</v>
       </c>
       <c r="B37" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>135710607</v>
       </c>
       <c r="B38" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>135710624</v>
       </c>
       <c r="B39" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>135710632</v>
       </c>
       <c r="B40" t="n">
-        <v>79472</v>
+        <v>79473</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135710600</v>
       </c>
       <c r="B2" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135710603</v>
       </c>
       <c r="B3" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135710605</v>
       </c>
       <c r="B4" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135710614</v>
       </c>
       <c r="B5" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135710617</v>
       </c>
       <c r="B6" t="n">
-        <v>96515</v>
+        <v>96526</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135710620</v>
       </c>
       <c r="B7" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135710601</v>
       </c>
       <c r="B8" t="n">
-        <v>93376</v>
+        <v>93382</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135710622</v>
       </c>
       <c r="B9" t="n">
-        <v>93376</v>
+        <v>93382</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135710604</v>
       </c>
       <c r="B10" t="n">
-        <v>93061</v>
+        <v>93067</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>135710625</v>
       </c>
       <c r="B11" t="n">
-        <v>79207</v>
+        <v>79211</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>135710602</v>
       </c>
       <c r="B12" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>135710623</v>
       </c>
       <c r="B13" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>135710627</v>
       </c>
       <c r="B14" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>135710631</v>
       </c>
       <c r="B15" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>135710612</v>
       </c>
       <c r="B16" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>135710629</v>
       </c>
       <c r="B17" t="n">
-        <v>78454</v>
+        <v>78458</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>135710608</v>
       </c>
       <c r="B28" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>135710610</v>
       </c>
       <c r="B29" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>135710618</v>
       </c>
       <c r="B30" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135710611</v>
       </c>
       <c r="B31" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>135710616</v>
       </c>
       <c r="B32" t="n">
-        <v>99325</v>
+        <v>99336</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>135710606</v>
       </c>
       <c r="B33" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>135710613</v>
       </c>
       <c r="B34" t="n">
-        <v>99109</v>
+        <v>99120</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>135710626</v>
       </c>
       <c r="B35" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>135710628</v>
       </c>
       <c r="B36" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>135710630</v>
       </c>
       <c r="B37" t="n">
-        <v>79208</v>
+        <v>79212</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>135710607</v>
       </c>
       <c r="B38" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>135710624</v>
       </c>
       <c r="B39" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>135710632</v>
       </c>
       <c r="B40" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135710600</v>
       </c>
       <c r="B2" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135710603</v>
       </c>
       <c r="B3" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135710605</v>
       </c>
       <c r="B4" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135710614</v>
       </c>
       <c r="B5" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135710617</v>
       </c>
       <c r="B6" t="n">
-        <v>96526</v>
+        <v>96539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135710620</v>
       </c>
       <c r="B7" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135710601</v>
       </c>
       <c r="B8" t="n">
-        <v>93382</v>
+        <v>93389</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135710622</v>
       </c>
       <c r="B9" t="n">
-        <v>93382</v>
+        <v>93389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135710604</v>
       </c>
       <c r="B10" t="n">
-        <v>93067</v>
+        <v>93074</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>135710625</v>
       </c>
       <c r="B11" t="n">
-        <v>79211</v>
+        <v>79217</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1853,7 +1853,7 @@
         <v>135710602</v>
       </c>
       <c r="B12" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>135710623</v>
       </c>
       <c r="B13" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>135710627</v>
       </c>
       <c r="B14" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>135710631</v>
       </c>
       <c r="B15" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>135710612</v>
       </c>
       <c r="B16" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2433,7 +2433,7 @@
         <v>135710629</v>
       </c>
       <c r="B17" t="n">
-        <v>78458</v>
+        <v>78464</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2549,7 +2549,7 @@
         <v>135710595</v>
       </c>
       <c r="B18" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>135710597</v>
       </c>
       <c r="B19" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         <v>135710633</v>
       </c>
       <c r="B20" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>135710634</v>
       </c>
       <c r="B21" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>135710635</v>
       </c>
       <c r="B22" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>135710594</v>
       </c>
       <c r="B23" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3303,7 +3303,7 @@
         <v>135710596</v>
       </c>
       <c r="B24" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>135710615</v>
       </c>
       <c r="B25" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3555,7 +3555,7 @@
         <v>135710619</v>
       </c>
       <c r="B26" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3681,7 +3681,7 @@
         <v>135710621</v>
       </c>
       <c r="B27" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>135710608</v>
       </c>
       <c r="B28" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>135710610</v>
       </c>
       <c r="B29" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>135710618</v>
       </c>
       <c r="B30" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135710611</v>
       </c>
       <c r="B31" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>135710616</v>
       </c>
       <c r="B32" t="n">
-        <v>99336</v>
+        <v>99349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>135710606</v>
       </c>
       <c r="B33" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>135710613</v>
       </c>
       <c r="B34" t="n">
-        <v>99120</v>
+        <v>99133</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4619,7 +4619,7 @@
         <v>135710626</v>
       </c>
       <c r="B35" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4735,7 +4735,7 @@
         <v>135710628</v>
       </c>
       <c r="B36" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4851,7 +4851,7 @@
         <v>135710630</v>
       </c>
       <c r="B37" t="n">
-        <v>79212</v>
+        <v>79218</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4967,7 +4967,7 @@
         <v>135710607</v>
       </c>
       <c r="B38" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>135710624</v>
       </c>
       <c r="B39" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>135710632</v>
       </c>
       <c r="B40" t="n">
-        <v>79477</v>
+        <v>79483</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 29267-2026 artfynd.xlsx
+++ b/artfynd/A 29267-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135710600</v>
       </c>
       <c r="B2" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135710603</v>
       </c>
       <c r="B3" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135710605</v>
       </c>
       <c r="B4" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135710614</v>
       </c>
       <c r="B5" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135710617</v>
       </c>
       <c r="B6" t="n">
-        <v>96539</v>
+        <v>96540</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135710620</v>
       </c>
       <c r="B7" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135710601</v>
       </c>
       <c r="B8" t="n">
-        <v>93389</v>
+        <v>93390</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>135710622</v>
       </c>
       <c r="B9" t="n">
-        <v>93389</v>
+        <v>93390</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1616,7 +1616,7 @@
         <v>135710604</v>
       </c>
       <c r="B10" t="n">
-        <v>93074</v>
+        <v>93075</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
         <v>135710608</v>
       </c>
       <c r="B28" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3923,7 +3923,7 @@
         <v>135710610</v>
       </c>
       <c r="B29" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>135710618</v>
       </c>
       <c r="B30" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4155,7 +4155,7 @@
         <v>135710611</v>
       </c>
       <c r="B31" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         <v>135710616</v>
       </c>
       <c r="B32" t="n">
-        <v>99349</v>
+        <v>99350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4387,7 +4387,7 @@
         <v>135710606</v>
       </c>
       <c r="B33" t="n">
-        <v>99133</v>
+        <v>99134</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4503,7 +4503,7 @@
         <v>135710613</v>
       </c>
       <c r="B34" t="n">
-        <v>99133</v>
+        <v>99134</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
